--- a/basic_data/template/plan/Amazon_Shipment_CA.xlsx
+++ b/basic_data/template/plan/Amazon_Shipment_CA.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16160" activeTab="2"/>
+    <workbookView windowWidth="32460" windowHeight="16160" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="71">
   <si>
     <t>如何使用 Send to Amazon 文件上传</t>
   </si>
@@ -261,7 +261,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="40">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -294,6 +294,11 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <name val="Amazon Ember"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="13"/>
       <name val="Amazon Ember"/>
       <charset val="134"/>
@@ -343,6 +348,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
       <name val="等线"/>
@@ -736,7 +746,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -922,37 +932,6 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1134,28 +1113,19 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1164,121 +1134,130 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1312,87 +1291,93 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1401,24 +1386,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="19" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2112,8 +2097,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="19.2"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="19.2" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="26.5" style="4" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="4" customWidth="1"/>
@@ -2130,39 +2115,37 @@
     <col min="13" max="16384" width="11" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="25" customFormat="1" ht="28.5" customHeight="1" spans="1:12">
-      <c r="A1" s="26" t="s">
+    <row r="1" s="26" customFormat="1" ht="28.5" customHeight="1" spans="1:12">
+      <c r="A1" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="27"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="28"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
+      <c r="A2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:12">
       <c r="A3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>23</v>
-      </c>
+      <c r="B3" s="9"/>
       <c r="C3" s="10"/>
       <c r="D3" s="11"/>
       <c r="F3" s="12"/>
@@ -2177,9 +2160,7 @@
       <c r="A4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>23</v>
-      </c>
+      <c r="B4" s="9"/>
       <c r="C4" s="10"/>
       <c r="D4" s="11"/>
       <c r="F4" s="12"/>
@@ -2219,102 +2200,60 @@
       <c r="L6" s="12"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="17.25" customHeight="1" spans="1:12">
-      <c r="A7" s="29"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30" t="s">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="30" t="s">
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="34"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="31"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="37.5" customHeight="1" spans="1:12">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="36" t="s">
+      <c r="H8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="36" t="s">
+      <c r="I8" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="36" t="s">
+      <c r="J8" s="35" t="s">
         <v>53</v>
       </c>
       <c r="K8" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="36" t="s">
+      <c r="L8" s="37" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="37"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="37"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="37"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2479,156 +2418,180 @@
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:12">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="24">
         <v>23</v>
       </c>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:12">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="24">
         <v>12</v>
       </c>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:12">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="24">
         <v>30</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="24">
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25">
         <v>45709</v>
       </c>
       <c r="F11" s="2">
         <v>123456789</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="24">
         <v>10</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="24">
         <v>3</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="24">
         <v>12.5</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="24">
         <v>12.5</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="24">
         <v>12.5</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="24">
         <v>3</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:12">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="24">
         <v>75</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="24">
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="25">
         <v>45709</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="24">
         <v>15</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="24">
         <v>5</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="24">
         <v>14.5</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="24">
         <v>10</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="24">
         <v>8.3</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="24">
         <v>5</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:12">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="24">
         <v>80</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="24">
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="25">
         <v>45798</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="24">
         <v>20</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="24">
         <v>4</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="24">
         <v>14.5</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="24">
         <v>10</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="24">
         <v>8.3</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="24">
         <v>5</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="24.95" customHeight="1" spans="1:12">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="24">
         <v>50</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="24">
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="25">
         <v>45829</v>
       </c>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="24">
         <v>30</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="G15" s="2">
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="G15" s="24">
         <v>10</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="24">
         <v>3</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="24">
         <v>12.5</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="24">
         <v>12.5</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="24">
         <v>12.5</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" s="24">
         <v>3</v>
       </c>
     </row>
